--- a/kinds_Read_EPS.xlsx
+++ b/kinds_Read_EPS.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mục lục" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL.md" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="320001" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="320002" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="320003" sheetId="5" state="visible" r:id="rId5"/>
@@ -536,6 +536,8 @@
           <t>Danh sách nội dung — Read_EPS</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -750,6 +752,11 @@
           <t>Kind: 3420006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -757,6 +764,11 @@
           <t>KIND 3420006 — Chủ đề đoạn văn (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -764,6 +776,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -867,6 +884,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -881,6 +903,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -936,6 +963,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -994,6 +1026,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1029,6 +1066,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -1064,6 +1106,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -1106,6 +1153,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -1201,6 +1253,11 @@
           <t>Kind: 3420007</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1208,6 +1265,11 @@
           <t>KIND 3420007 — Nội dung khớp (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1215,6 +1277,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1318,6 +1385,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1332,6 +1404,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -1387,6 +1464,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -1479,6 +1561,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -1514,6 +1601,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -1542,6 +1634,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -1591,6 +1688,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -1686,6 +1788,11 @@
           <t>Kind: 3420008</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1693,6 +1800,11 @@
           <t>KIND 3420008 — Từ vựng theo mô tả (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1700,6 +1812,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1803,6 +1920,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1817,6 +1939,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -1872,6 +1999,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -1930,6 +2062,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1958,6 +2095,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -1986,6 +2128,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2028,6 +2175,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2121,6 +2273,11 @@
           <t>SKILL.md — Read_EPS</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2128,6 +2285,11 @@
           <t>EPS-TOPIK Reading Question Generator (Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -2142,6 +2304,11 @@
           <t>Khi nào dùng skill này</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -2170,6 +2337,11 @@
           <t>Cấu trúc thư mục</t>
         </is>
       </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2303,6 +2475,11 @@
           <t>Output Format (JSON)</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -2718,6 +2895,11 @@
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="13" t="inlineStr">
@@ -2984,6 +3166,11 @@
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="10" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="13" t="inlineStr">
@@ -3281,6 +3468,11 @@
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
+      <c r="B132" s="10" t="n"/>
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="10" t="n"/>
+      <c r="F132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
@@ -3515,6 +3707,11 @@
           <t>Định dạng văn bản đọc (text_format)</t>
         </is>
       </c>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="10" t="n"/>
+      <c r="F145" s="10" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
@@ -3683,6 +3880,11 @@
           <t>Ngữ pháp đáp án (answer_grammar)</t>
         </is>
       </c>
+      <c r="B155" s="10" t="n"/>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="10" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
@@ -3782,6 +3984,11 @@
           <t>Thang độ khó (Difficulty Scale)</t>
         </is>
       </c>
+      <c r="B163" s="10" t="n"/>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="10" t="n"/>
+      <c r="F163" s="10" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
@@ -3915,6 +4122,11 @@
           <t>Cấp độ đọc EPS (reading_level)</t>
         </is>
       </c>
+      <c r="B173" s="10" t="n"/>
+      <c r="C173" s="10" t="n"/>
+      <c r="D173" s="10" t="n"/>
+      <c r="E173" s="10" t="n"/>
+      <c r="F173" s="10" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
@@ -3963,6 +4175,11 @@
           <t>Quy tắc chung khi gen câu hỏi</t>
         </is>
       </c>
+      <c r="B178" s="10" t="n"/>
+      <c r="C178" s="10" t="n"/>
+      <c r="D178" s="10" t="n"/>
+      <c r="E178" s="10" t="n"/>
+      <c r="F178" s="10" t="n"/>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="13" t="inlineStr">
@@ -4166,6 +4383,11 @@
           <t>Workflow</t>
         </is>
       </c>
+      <c r="B207" s="10" t="n"/>
+      <c r="C207" s="10" t="n"/>
+      <c r="D207" s="10" t="n"/>
+      <c r="E207" s="10" t="n"/>
+      <c r="F207" s="10" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -4434,6 +4656,11 @@
           <t>Kind: 320001</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4441,6 +4668,11 @@
           <t>KIND 320001 — Xem hình chọn từ/câu (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4455,6 +4687,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4558,6 +4795,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -4572,6 +4814,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -4627,6 +4874,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4668,6 +4920,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -4703,6 +4960,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -4731,6 +4993,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -4773,6 +5040,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -4868,6 +5140,11 @@
           <t>Kind: 320002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4875,6 +5152,11 @@
           <t>KIND 320002 — Điền chỗ trống (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4889,6 +5171,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4992,6 +5279,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -5006,6 +5298,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -5061,6 +5358,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -5136,6 +5438,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -5171,6 +5478,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -5199,6 +5511,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -5241,6 +5558,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -5336,6 +5658,11 @@
           <t>Kind: 320003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5343,6 +5670,11 @@
           <t>KIND 320003 — Trả lời câu hỏi — hình (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5357,6 +5689,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5460,6 +5797,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -5474,6 +5816,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -5529,6 +5876,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -5587,6 +5939,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -5622,6 +5979,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -5657,6 +6019,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -5699,6 +6066,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -5795,6 +6167,11 @@
           <t>Kind: 320004</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5802,6 +6179,11 @@
           <t>KIND 320004 — Đọc + trả lời (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5809,6 +6191,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -5912,6 +6299,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5926,6 +6318,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -5981,6 +6378,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -6056,6 +6458,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -6091,6 +6498,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -6119,6 +6531,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -6168,6 +6585,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -6263,6 +6685,11 @@
           <t>Kind: 320005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -6270,6 +6697,11 @@
           <t>KIND 320005 — Đọc dài + 2 câu hỏi (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -6277,6 +6709,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -6380,6 +6817,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6394,6 +6836,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -6449,6 +6896,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -6524,6 +6976,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -6566,6 +7023,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -6601,6 +7063,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -6650,6 +7117,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -6763,6 +7235,11 @@
           <t>Kind: 3420002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -6770,6 +7247,11 @@
           <t>KIND 3420002 — Từ liên quan (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -6777,6 +7259,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -6880,6 +7367,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6894,6 +7386,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -6949,6 +7446,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -6990,6 +7492,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -7018,6 +7525,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -7046,6 +7558,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -7088,6 +7605,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -7181,6 +7703,11 @@
           <t>Kind: 3420003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -7188,6 +7715,11 @@
           <t>KIND 3420003 — Đồng nghĩa / trái nghĩa (EPS-TOPIK, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -7195,6 +7727,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -7298,6 +7835,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -7312,6 +7854,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -7367,6 +7914,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -7425,6 +7977,11 @@
           <t>Cấu trúc bài đọc</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -7453,6 +8010,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -7488,6 +8050,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7530,6 +8097,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">

--- a/kinds_Read_EPS.xlsx
+++ b/kinds_Read_EPS.xlsx
@@ -2256,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2617,7 +2617,7 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "vi": "&lt;giải thích tiếng Việt&gt;",</t>
+          <t xml:space="preserve">        "vi": "&lt;giải thích tiếng Việt — GHI RÕ trap type cho từng đáp án sai&gt;",</t>
         </is>
       </c>
     </row>
@@ -2631,112 +2631,105 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      },</t>
+          <t xml:space="preserve">      }</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "question_feature": "&lt;mã đặc điểm từ bảng question_feature&gt;",</t>
+          <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "difficulty": &lt;mức độ khó 1-4&gt;,</t>
+          <t xml:space="preserve">  ],</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "distractor_traps": {</t>
+          <t xml:space="preserve">  "level": 3,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "1": "&lt;trap code cho đáp án 1 — rỗng nếu là đáp án đúng&gt;",</t>
+          <t xml:space="preserve">  "kind": "320001",</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "2": "&lt;trap code cho đáp án 2&gt;",</t>
+          <t xml:space="preserve">  "count_question": 1,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "3": "&lt;trap code cho đáp án 3&gt;",</t>
+          <t xml:space="preserve">  "tag": "read"</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "4": "&lt;trap code cho đáp án 4&gt;"</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      }</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    }</t>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>Trường tùy chọn (OPTIONAL — chỉ thêm nếu cần phân tích chuyên sâu)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ],</t>
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Các trường sau KHÔNG bắt buộc khi gen câu hỏi. Samples.json không chứa các trường này. Chỉ thêm khi user yêu cầu phân tích metadata:</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "level": 3,</t>
+          <t>// Trong content[]:</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "kind": "320001",</t>
+          <t>"question_feature": "&lt;mã từ bảng question_feature&gt;",</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "count_question": 1,</t>
+          <t>"difficulty": 3,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "tag": "read",</t>
+          <t>"distractor_traps": {</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "topic": "&lt;mã chủ đề từ bảng topic&gt;"</t>
+          <t xml:space="preserve">  "1": "", "2": "trap_detail_distort", "3": "trap_neg_없안", "4": "trap_shared_noun"</t>
         </is>
       </c>
     </row>
@@ -2747,643 +2740,671 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>// Ở cấp top-level:</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>"topic": "daily_routine"</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Lưu ý riêng EPS-TOPIK</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>Trường</t>
         </is>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>EPS-TOPIK</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>`level`</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>**Luôn = 3**</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>`q_point`</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>**null** (EPS không tính điểm theo câu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>`count_question`</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>**null** hoặc khớp len(content)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>`tag`</t>
+          <t>`level`</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>`"read"`</t>
+          <t>**Luôn = 3**</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
+          <t>`q_point`</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>**null** (EPS không tính điểm theo câu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>`count_question`</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>**Luôn là integer** = len(content). VD: 1 cho câu đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>`tag`</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>`"read"`</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
           <t>`q_image`</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>URL ảnh thực (poster, biển hiệu, hình minh họa)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="13" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Format bổ sung cho kind có ảnh</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>Thêm trường q_image_description mô tả nội dung ảnh bằng text:</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": {</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "image": "&lt;mô tả chi tiết nội dung hình ảnh&gt;"</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  "q_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "&lt;mô tả chi tiết nội dung hình ảnh&gt;"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>Áp dụng cho: 320001, 320003, 320004, 3420001, 3420005.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ Lưu ý: q_image_description là trường chỉ dùng khi gen câu hỏi mới — dùng để mô tả ảnh bằng text cho AI tạo ảnh sau. Trường này KHÔNG có trong samples.json (vì samples lấy từ dữ liệu thực đã có ảnh URL). Đặt ở cấp top-level của JSON (cùng cấp với title, general).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>Chủ đề riêng EPS-TOPIK (Level 3)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="14" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
         <is>
           <t>Kind chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>`factory_work`</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Factory &amp; Production</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>320002, 3420004</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>`dormitory_life`</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Dormitory Life</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>320003, 3420005</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>`safety_workplace`</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Workplace Safety</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>320003, 3420007</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>`wages_contract`</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Wages &amp; Contract</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>320004, 3420004</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>`korean_culture`</t>
+          <t>`factory_work`</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Korean Culture &amp; Etiquette</t>
+          <t>Factory &amp; Production</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>3420006, 3420007</t>
+          <t>320002, 3420004</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>`daily_vocab`</t>
+          <t>`dormitory_life`</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Daily Vocabulary</t>
+          <t>Dormitory Life</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>320001, 3420001, 3420002, 3420008</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="13" t="inlineStr">
-        <is>
-          <t>Chủ đề chung (dùng được cho EPS)</t>
+          <t>320003, 3420005</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>`safety_workplace`</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Workplace Safety</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>320003, 3420007</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>`wages_contract`</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Wages &amp; Contract</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>320004, 3420004</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>Tiếng Hàn</t>
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>`korean_culture`</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Korean Culture &amp; Etiquette</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>3420006, 3420007</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>`daily_life`</t>
+          <t>`daily_vocab`</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Daily Life &amp; Routine</t>
+          <t>Daily Vocabulary</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>일상생활</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>`food_restaurant`</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Food &amp; Dining</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>음식/식당</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>`shopping_price`</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Shopping &amp; Price</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>쇼핑/가격</t>
+          <t>320001, 3420001, 3420002, 3420008</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>Chủ đề chung (dùng được cho EPS)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>`health_hospital`</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Health &amp; Hospital</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>건강/병원</t>
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>`weather_season`</t>
+          <t>`daily_life`</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Weather &amp; Seasons</t>
+          <t>Daily Life &amp; Routine</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>날씨/계절</t>
+          <t>일상생활</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>`food_restaurant`</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Food &amp; Dining</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>음식/식당</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>`shopping_price`</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Shopping &amp; Price</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>쇼핑/가격</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>`health_hospital`</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Health &amp; Hospital</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>건강/병원</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>`weather_season`</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Weather &amp; Seasons</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>날씨/계절</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
           <t>`travel`</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Travel &amp; Tourism</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>여행/관광</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="9" t="inlineStr">
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
-      <c r="B107" s="10" t="n"/>
-      <c r="C107" s="10" t="n"/>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="13" t="inlineStr">
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="10" t="n"/>
+      <c r="F111" s="10" t="n"/>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="13" t="inlineStr">
         <is>
           <t>Nhóm 1: Bẫy từ vựng (Vocabulary Traps)</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="14" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B109" s="14" t="inlineStr">
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C109" s="14" t="inlineStr">
+      <c r="C113" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Similar Word</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án chứa từ phát âm/dạng tương tự</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>320001, 320002, 3420002, 3420003, 3420006, 3420008</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>`trap_shared_noun`</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Shared-Noun Trap</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>Đáp án sai chứa từ vựng giống đoạn đọc</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>`trap_synonym_swap`</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Synonym Swap</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Thay từ đúng bằng từ đồng nghĩa nhưng sai ngữ cảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>`trap_similar_word`</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>Similar Word</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án chứa từ phát âm/dạng tương tự (e.g. 관광/관계)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 2: Bẫy phủ định (Negation Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>320002, 3420006, 3420008</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>`trap_neg_없안`</t>
+          <t>`trap_synonym_swap`</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Negation 없/안/아니</t>
+          <t>Synonym Swap</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Đáp án sai đảo nghĩa bằng 없다/안/아니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>`trap_neg_않못`</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Negation 않/못</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án sai thêm 않다/못하다</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 3: Bẫy cấu trúc (Structural Traps)</t>
+          <t>Thay từ đúng bằng từ đồng nghĩa nhưng sai ngữ cảnh</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>320002, 3420003</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 2: Bẫy phủ định (Negation Traps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B120" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C120" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>`trap_neg_reverse`</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Negation Reverse</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Đảo nghĩa phủ định</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>320005</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>`trap_same_ending`</t>
+          <t>`trap_neg_없안`</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Same-Ending Pattern</t>
+          <t>Negation 없/안/아니</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Cả 4 đáp án kết thúc cùng dạng ngữ pháp</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>`trap_same_length`</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>Same-Length Pattern</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án cùng độ dài, khó phân biệt bằng mắt</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 4: Bẫy nội dung (Content Traps)</t>
+          <t>Đáp án sai đảo nghĩa bằng 없다/안</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>3420007</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 3: Bẫy nội dung (Content Traps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B125" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Detail Distortion</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Bóp méo chi tiết nhỏ</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>320003, 320004, 320005, 3420007</t>
         </is>
       </c>
     </row>
@@ -3400,443 +3421,463 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Đáp án sai chứa &gt;50% nội dung đúng nhưng sửa 1 chi tiết</t>
+          <t>Đáp án sai chứa &gt;50% nội dung đúng</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>320004, 320005, 3420007</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>`trap_subject_swap`</t>
+          <t>`trap_number_shift`</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Subject Swap</t>
+          <t>Number/Time Shift</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Gán hành động/đặc điểm cho sai đối tượng</t>
+          <t>Thay đổi con số/thời gian</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>320004</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>`trap_number_shift`</t>
+          <t>`trap_subject_swap`</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Number/Time Shift</t>
+          <t>Subject Swap</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Thay đổi con số/thời gian/số lượng từ bài đọc</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>`trap_detail_distort`</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>Detail Distortion</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án sai bóp méo chi tiết nhỏ trong đoạn văn</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
+          <t>Gán hành động cho sai đối tượng</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>3420007</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
-      <c r="B132" s="10" t="n"/>
-      <c r="C132" s="10" t="n"/>
-      <c r="D132" s="10" t="n"/>
-      <c r="E132" s="10" t="n"/>
-      <c r="F132" s="10" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="10" t="n"/>
+      <c r="F131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B133" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C133" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D133" s="14" t="inlineStr">
-        <is>
-          <t>Kind áp dụng</t>
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>`qf_image_word`</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Image → Word/Sentence</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Nhìn hình chọn từ/câu mô tả</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>320001, 3420001</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>`qf_image_word`</t>
+          <t>`qf_image_qa`</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Image → Word/Sentence</t>
+          <t>Image Q&amp;A</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Nhìn hình chọn từ/câu mô tả</t>
+          <t>Nhìn hình + đọc câu hỏi → chọn đáp án</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>320001, 3420001</t>
+          <t>320003, 320004, 3420005</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>`qf_image_qa`</t>
+          <t>`qf_fill_blank`</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Image Q&amp;A</t>
+          <t>Fill in Blank</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Nhìn hình + đọc câu hỏi → chọn đáp án</t>
+          <t>Điền từ/cụm vào chỗ trống ( )</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>320003, 320004, 3420005</t>
+          <t>320002, 3420004</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>`qf_fill_blank`</t>
+          <t>`qf_word_relation`</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Fill in Blank</t>
+          <t>Word Relationship</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Điền từ/cụm vào chỗ trống ( )</t>
+          <t>Tìm từ liên quan</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>320002, 3420004</t>
+          <t>3420002</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>`qf_word_relation`</t>
+          <t>`qf_synonym_antonym`</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Word Relationship</t>
+          <t>Synonym/Antonym</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Tìm từ liên quan</t>
+          <t>Tìm từ đồng nghĩa hoặc trái nghĩa</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>3420002</t>
+          <t>3420003</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>`qf_synonym_antonym`</t>
+          <t>`qf_vocab_definition`</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Synonym/Antonym</t>
+          <t>Vocabulary Definition</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Tìm từ đồng nghĩa hoặc trái nghĩa</t>
+          <t>Đọc mô tả, chọn từ phù hợp</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>3420003</t>
+          <t>3420008</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>`qf_vocab_definition`</t>
+          <t>`qf_topic_identify`</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Vocabulary Definition</t>
+          <t>Topic Identification</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Đọc mô tả, chọn từ phù hợp</t>
+          <t>Đoạn văn nói về chủ đề gì?</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>3420008</t>
+          <t>3420006</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>`qf_topic_identify`</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Topic Identification</t>
+          <t>Content Matching</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn nói về chủ đề gì?</t>
+          <t>Chọn phát biểu khớp nội dung</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>3420006</t>
+          <t>3420007</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>`qf_content_match`</t>
+          <t>`qf_multi_passage`</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Content Matching</t>
+          <t>Multi-Question Passage</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Chọn phát biểu khớp nội dung</t>
+          <t>Đoạn văn + 2 câu hỏi</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>3420007</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>`qf_multi_passage`</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>Multi-Question Passage</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn văn + 2 câu hỏi</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
           <t>320005</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Định dạng văn bản đọc (text_format)</t>
         </is>
       </c>
-      <c r="B145" s="10" t="n"/>
-      <c r="C145" s="10" t="n"/>
-      <c r="D145" s="10" t="n"/>
-      <c r="E145" s="10" t="n"/>
-      <c r="F145" s="10" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="10" t="n"/>
+      <c r="F144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>Độ dài trung bình</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>Kind chính</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B146" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="C146" s="14" t="inlineStr">
-        <is>
-          <t>Độ dài trung bình</t>
-        </is>
-      </c>
-      <c r="D146" s="14" t="inlineStr">
-        <is>
-          <t>Kind chính</t>
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>`text_dialog_eps`</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Hội thoại 가/나 ngắn (EPS)</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>30-80 ký tự</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>320002, 3420004</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>`text_dialog_eps`</t>
+          <t>`text_image_only`</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Hội thoại 가/나 ngắn (EPS)</t>
+          <t>Chỉ có hình, không text</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>30-80 ký tự</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>320002, 3420004</t>
+          <t>320001, 3420001, 320003</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>`text_image_only`</t>
+          <t>`text_single_word`</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Chỉ có hình, không text</t>
+          <t>Từ đơn hoặc cụm ngắn</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>2-10 ký tự</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>320001, 3420001, 320003</t>
+          <t>3420002, 3420003, 3420008</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>`text_single_word`</t>
+          <t>`text_paragraph_short`</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Từ đơn hoặc cụm ngắn</t>
+          <t>Đoạn văn ngắn (3-5 câu)</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>2-10 ký tự</t>
+          <t>50-100 ký tự</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>3420002, 3420003, 3420008</t>
+          <t>320004, 3420006, 3420007</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>`text_paragraph_short`</t>
+          <t>`text_paragraph_long`</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn ngắn (3-5 câu)</t>
+          <t>Đoạn văn dài (6+ câu)</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>50-100 ký tự</t>
+          <t>150-300 ký tự</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>320004, 3420006, 3420007</t>
+          <t>320005</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>`text_paragraph_long`</t>
+          <t>`text_passage_multi`</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn dài (6+ câu)</t>
+          <t>Đoạn dài + nhiều câu hỏi</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>150-300 ký tự</t>
+          <t>150-500 ký tự (g_text)</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -3845,603 +3886,564 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>`text_passage_multi`</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn dài + nhiều câu hỏi</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>150-500 ký tự (g_text)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>320005</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="11" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="9" t="inlineStr">
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="9" t="inlineStr">
         <is>
           <t>Ngữ pháp đáp án (answer_grammar)</t>
         </is>
       </c>
-      <c r="B155" s="10" t="n"/>
-      <c r="C155" s="10" t="n"/>
-      <c r="D155" s="10" t="n"/>
-      <c r="E155" s="10" t="n"/>
-      <c r="F155" s="10" t="n"/>
+      <c r="B154" s="10" t="n"/>
+      <c r="C154" s="10" t="n"/>
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="10" t="n"/>
+      <c r="F154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B156" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="C156" s="14" t="inlineStr">
-        <is>
-          <t>Kind áp dụng</t>
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>`ans_noun_phrase`</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là danh từ/cụm danh từ</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>320001, 320002, 320003, 320004, 320005, 3420002, 3420003, 3420006, 3420008</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>`ans_noun_phrase`</t>
+          <t>`ans_sentence_long`</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Đáp án là danh từ/cụm danh từ</t>
+          <t>Đáp án là câu dài (20+ ký tự)</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>320001, 3420001, 3420002, 3420003, 3420008</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>`ans_sentence_polite`</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án dùng ~ㅂ니다/습니다</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>320004, 3420007</t>
+          <t>3420007</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>`ans_sentence_plain`</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là câu thể trần thuật</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>3420006</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>`ans_grammar_form`</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là cấu trúc ngữ pháp</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Thang độ khó (Difficulty Scale)</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n"/>
+      <c r="C160" s="10" t="n"/>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="14" t="inlineStr">
+        <is>
+          <t>Mức</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>Kiểu suy luận</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>320001, 3420001</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>`image_recognition` — Nhận diện từ qua hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>3420002, 3420003, 3420008</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>`vocab_match` — Từ vựng đơn giản</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
         <is>
           <t>320002, 3420004</t>
         </is>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>Thang độ khó (Difficulty Scale)</t>
-        </is>
-      </c>
-      <c r="B163" s="10" t="n"/>
-      <c r="C163" s="10" t="n"/>
-      <c r="D163" s="10" t="n"/>
-      <c r="E163" s="10" t="n"/>
-      <c r="F163" s="10" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="14" t="inlineStr">
-        <is>
-          <t>Mức</t>
-        </is>
-      </c>
-      <c r="B164" s="14" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="C164" s="14" t="inlineStr">
-        <is>
-          <t>Kiểu suy luận</t>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>`context_fill` — Điền chỗ trống dựa ngữ cảnh</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>320001, 3420001</t>
+          <t>320003, 3420005, 3420006</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>`image_recognition` — Nhận diện từ qua hình</t>
+          <t>`detail_extraction` — Trích xuất chi tiết từ hình/văn</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>3420002, 3420003, 3420008</t>
+          <t>3420007</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>`vocab_match` — Từ vựng đơn giản</t>
+          <t>`content_matching` — So khớp nội dung</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>320002, 3420004</t>
+          <t>320004, 320005</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>`context_fill` — Điền chỗ trống dựa ngữ cảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>320003, 3420005, 3420006</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>`detail_extraction` — Trích xuất chi tiết từ hình/văn</t>
+          <t>`paragraph_comprehension` — Hiểu đoạn văn</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>3420007</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>`content_matching` — So khớp nội dung</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>320004, 320005</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>`paragraph_comprehension` — Hiểu đoạn văn</t>
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>Cấp độ đọc EPS (reading_level)</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n"/>
+      <c r="C170" s="10" t="n"/>
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="10" t="n"/>
+      <c r="F170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="14" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B171" s="14" t="inlineStr">
+        <is>
+          <t>Đặc điểm văn bản</t>
+        </is>
+      </c>
+      <c r="C171" s="14" t="inlineStr">
+        <is>
+          <t>Ngữ pháp phổ biến</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="11" t="inlineStr">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>3 (EPS)</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Đoạn ngắn-trung bình, từ vựng thực tế lao động</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>~(으)면, ~어야 하다, ~지 마십시오, ~(으)세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>Cấp độ đọc EPS (reading_level)</t>
-        </is>
-      </c>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="10" t="n"/>
-      <c r="D173" s="10" t="n"/>
-      <c r="E173" s="10" t="n"/>
-      <c r="F173" s="10" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="14" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B174" s="14" t="inlineStr">
-        <is>
-          <t>Đặc điểm văn bản</t>
-        </is>
-      </c>
-      <c r="C174" s="14" t="inlineStr">
-        <is>
-          <t>Ngữ pháp phổ biến</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>3 (EPS)</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn ngắn-trung bình, từ vựng thực tế lao động</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>~(으)면, ~어야 하다, ~지 마십시오, ~(으)세요</t>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc chung khi gen câu hỏi</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="n"/>
+      <c r="C175" s="10" t="n"/>
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="10" t="n"/>
+      <c r="F175" s="10" t="n"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>1. Chất lượng nội dung tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc chung khi gen câu hỏi</t>
-        </is>
-      </c>
-      <c r="B178" s="10" t="n"/>
-      <c r="C178" s="10" t="n"/>
-      <c r="D178" s="10" t="n"/>
-      <c r="E178" s="10" t="n"/>
-      <c r="F178" s="10" t="n"/>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="13" t="inlineStr">
-        <is>
-          <t>1. Chất lượng nội dung tiếng Hàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="11" t="inlineStr">
-        <is>
           <t>• Dùng ngữ pháp đúng level EPS (xem bảng reading_level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>• Văn bản tự nhiên, đa dạng chủ đề (lao động, an toàn, ký túc xá, lương, văn hóa Hàn, từ vựng hàng ngày)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>2. Xây dựng đáp án sai (distractor)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>• Văn bản tự nhiên, đa dạng chủ đề (lao động, an toàn, ký túc xá, lương, văn hóa Hàn, từ vựng hàng ngày)</t>
+          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="13" t="inlineStr">
-        <is>
-          <t>2. Xây dựng đáp án sai (distractor)</t>
+          <t>• Phải hợp lý nhưng SAI về nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>• Tái sử dụng từ vựng bài đọc khi kind yêu cầu trap_shared_noun</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="11" t="inlineStr">
-        <is>
-          <t>• Phải hợp lý nhưng SAI về nội dung</t>
+          <t>• Đáp án sai phải cùng format/độ dài với đáp án đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="13" t="inlineStr">
+        <is>
+          <t>3. Giải thích (explain)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>• Tái sử dụng từ vựng bài đọc khi kind yêu cầu trap_shared_noun</t>
+          <t>• vi: Dịch bài đọc + dịch cả 4 đáp án → dấu -------------------- → giải thích đáp án đúng</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai phải cùng format/độ dài với đáp án đúng</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="13" t="inlineStr">
-        <is>
-          <t>3. Giải thích (explain)</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>• vi: Dịch bài đọc + dịch cả 4 đáp án → dấu -------------------- → giải thích đáp án đúng</t>
+          <t>• en: Tương tự bằng tiếng Anh</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="13" t="inlineStr">
+        <is>
+          <t>4. Số lượng</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>• en: Tương tự bằng tiếng Anh</t>
+          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
+          <t>• Tối đa: 20 câu mỗi lần</t>
         </is>
       </c>
     </row>
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>4. Số lượng</t>
+          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
+          <t>• [ ] q_correct nằm trong 1-4</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>• Tối đa: 20 câu mỗi lần</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="13" t="inlineStr">
-        <is>
-          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
+          <t>• [ ] 4 đáp án không trùng nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Văn bản là tiếng Hàn tự nhiên, đúng level EPS</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct nằm trong 1-4</t>
+          <t>• [ ] Bẫy đúng phân bố của kind</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>• [ ] 4 đáp án không trùng nhau</t>
+          <t>• [ ] Bản dịch (vi/en) chính xác</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Văn bản là tiếng Hàn tự nhiên, đúng level EPS</t>
+          <t>• [ ] explain chứa dịch + lý do đáp án đúng + ghi chú trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bẫy đúng phân bố của kind</t>
+          <t>• [ ] count_question khớp số phần tử trong content (hoặc null)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bản dịch (vi/en) chính xác</t>
+          <t>• [ ] tag = "read" (KHÔNG phải "listen")</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>• [ ] explain chứa dịch + lý do đáp án đúng + ghi chú trap type cho từng đáp án sai</t>
+          <t>• [ ] level = 3</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>• [ ] count_question khớp số phần tử trong content (hoặc null)</t>
+          <t>• [ ] q_point = null (EPS không tính điểm)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>• [ ] tag = "read" (KHÔNG phải "listen")</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] level = 3</t>
-        </is>
-      </c>
+          <t>• [ ] Kind có ảnh → có q_image_description</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="n"/>
+      <c r="C204" s="10" t="n"/>
+      <c r="D204" s="10" t="n"/>
+      <c r="E204" s="10" t="n"/>
+      <c r="F204" s="10" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_point = null (EPS không tính điểm)</t>
+          <t>1. User chỉ định kind → đọc file kinds/{kind}.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Kind có ảnh → có q_image_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="9" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-      <c r="B207" s="10" t="n"/>
-      <c r="C207" s="10" t="n"/>
-      <c r="D207" s="10" t="n"/>
-      <c r="E207" s="10" t="n"/>
-      <c r="F207" s="10" t="n"/>
+          <t>2. Hỏi số lượng (mặc định 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>1. User chỉ định kind → đọc file kinds/{kind}.md</t>
+          <t>4. Lưu JSON tạm → chạy scripts/save_read.py để tách CSV theo kind</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>2. Hỏi số lượng (mặc định 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="11" t="inlineStr">
-        <is>
-          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
+          <t>5. Validate theo checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="13" t="inlineStr">
+        <is>
+          <t>Lưu kết quả bằng script</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="inlineStr">
-        <is>
-          <t>4. Lưu JSON tạm → chạy scripts/save_read.py để tách CSV theo kind</t>
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t># Lưu CSV theo kind + JSON + merge tổng</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="11" t="inlineStr">
-        <is>
-          <t>5. Validate theo checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="13" t="inlineStr">
-        <is>
-          <t>Lưu kết quả bằng script</t>
-        </is>
-      </c>
+      <c r="A212" s="12" t="inlineStr">
+        <is>
+          <t>python skills/topik-read-gen-eps/scripts/save_read.py gen_temp.json -o output/read-eps --json --merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="12" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
         <is>
-          <t># Lưu CSV theo kind + JSON + merge tổng</t>
+          <t># Chỉ validate</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="12" t="inlineStr">
         <is>
-          <t>python skills/topik-read-gen-eps/scripts/save_read.py gen_temp.json -o output/read-eps --json --merge</t>
+          <t>python skills/topik-read-gen-eps/scripts/save_read.py gen_temp.json --validate-only</t>
         </is>
       </c>
     </row>
@@ -4451,46 +4453,32 @@
     <row r="217">
       <c r="A217" s="12" t="inlineStr">
         <is>
-          <t># Chỉ validate</t>
+          <t># Append thêm batch mới</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
         <is>
-          <t>python skills/topik-read-gen-eps/scripts/save_read.py gen_temp.json --validate-only</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="12" t="inlineStr"/>
+          <t>python skills/topik-read-gen-eps/scripts/save_read.py new_batch.json --append</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="12" t="inlineStr">
-        <is>
-          <t># Append thêm batch mới</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-read-gen-eps/scripts/save_read.py new_batch.json --append</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="11" t="inlineStr">
+      <c r="A220" s="11" t="inlineStr">
         <is>
           <t>Output: output/read-eps/level_3/{kind}.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="140">
+  <mergeCells count="142">
+    <mergeCell ref="A174:F174"/>
     <mergeCell ref="A205:F205"/>
     <mergeCell ref="A183:F183"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="A198:F198"/>
     <mergeCell ref="A50:F50"/>
@@ -4498,11 +4486,14 @@
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A144:F144"/>
-    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A159:F159"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="A81:F81"/>
@@ -4518,22 +4509,17 @@
     <mergeCell ref="A186:F186"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A172:F172"/>
     <mergeCell ref="A212:F212"/>
-    <mergeCell ref="A221:F221"/>
-    <mergeCell ref="A108:F108"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A214:F214"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A204:F204"/>
@@ -4548,29 +4534,29 @@
     <mergeCell ref="A215:F215"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A112:F112"/>
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A176:F176"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A216:F216"/>
     <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="A218:F218"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="A208:F208"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A154:F154"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A179:F179"/>
@@ -4585,46 +4571,47 @@
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A92:F92"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A193:F193"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A89:F89"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A192:F192"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A185:F185"/>
-    <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A194:F194"/>
-    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A211:F211"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A220:F220"/>
-    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A130:F130"/>
     <mergeCell ref="A201:F201"/>
-    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A123:F123"/>
     <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A119:F119"/>
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A25:F25"/>

--- a/kinds_Read_EPS.xlsx
+++ b/kinds_Read_EPS.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1 hoặc None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1 hoặc None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
